--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CIUDAD MOLINA BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CIUDAD MOLINA BASKET.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.303100000000001</v>
+        <v>6.2568</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2008</v>
+        <v>7.4275</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8977999999999999</v>
+        <v>-1.1707</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2719999999999998</v>
+        <v>0.2671999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.8314999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1273</v>
+        <v>1.0987</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4658</v>
+        <v>1.5886</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5674</v>
+        <v>0.6669999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8983000000000001</v>
+        <v>0.9216</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1937</v>
+        <v>-1.3214</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4227</v>
+        <v>-1.4985</v>
       </c>
       <c r="O2" t="n">
-        <v>0.229</v>
+        <v>0.1771</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8678</v>
+        <v>2.8344</v>
       </c>
       <c r="S2" t="n">
-        <v>3.355</v>
+        <v>3.3215</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9458</v>
+        <v>2.9651</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4092</v>
+        <v>0.3564</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8323</v>
+        <v>0.8461</v>
       </c>
       <c r="W2" t="n">
-        <v>3.8136</v>
+        <v>3.886</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.9812</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3421</v>
+        <v>5.4058</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5898</v>
+        <v>5.8407</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2476999999999998</v>
+        <v>-0.4348999999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8712</v>
+        <v>4.8928</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2483</v>
+        <v>1.2266</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6228</v>
+        <v>3.6662</v>
       </c>
       <c r="J3" t="n">
-        <v>5.781</v>
+        <v>5.9161</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8069</v>
+        <v>1.8557</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9741</v>
+        <v>4.060499999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9097999999999999</v>
+        <v>-1.0233</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5586</v>
+        <v>-0.6289</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3512</v>
+        <v>-0.3943</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6145</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6873</v>
+        <v>3.6441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3999</v>
+        <v>-1.3663</v>
       </c>
       <c r="T3" t="n">
-        <v>0.03609999999999997</v>
+        <v>0.07900000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.436</v>
+        <v>-1.4453</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2562</v>
+        <v>1.2719</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8454</v>
+        <v>2.8822</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5892</v>
+        <v>-1.6103</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9456</v>
+        <v>3.9147</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3437999999999999</v>
+        <v>0.5283</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6016</v>
+        <v>3.3864</v>
       </c>
       <c r="G4" t="n">
-        <v>2.015</v>
+        <v>1.9998</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8735</v>
+        <v>1.8965</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1416</v>
+        <v>0.1033</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9297</v>
+        <v>3.0256</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5992</v>
+        <v>2.684</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3307</v>
+        <v>0.3416</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9147</v>
+        <v>-1.0257</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7257</v>
+        <v>-0.7875000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.189</v>
+        <v>-0.2382</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4097000000000001</v>
+        <v>0.4049</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4824</v>
+        <v>3.4417</v>
       </c>
       <c r="S4" t="n">
-        <v>0.234</v>
+        <v>0.2266</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0027</v>
+        <v>0.0376</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2313</v>
+        <v>0.1889</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2868</v>
+        <v>1.2834</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8027</v>
+        <v>0.7815000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1616</v>
+        <v>2.109900000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8012</v>
+        <v>1.8721</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3603000000000001</v>
+        <v>0.2378</v>
       </c>
       <c r="G5" t="n">
-        <v>4.151</v>
+        <v>4.110399999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0236</v>
+        <v>-1.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1745</v>
+        <v>5.1758</v>
       </c>
       <c r="J5" t="n">
-        <v>3.865</v>
+        <v>3.8985</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5210999999999999</v>
+        <v>-0.5143000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>4.3862</v>
+        <v>4.412800000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2858999999999999</v>
+        <v>0.2119</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5024</v>
+        <v>-0.551</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7883999999999999</v>
+        <v>0.7629</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6282</v>
+        <v>-1.6202</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0396</v>
+        <v>-1.0141</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5885</v>
+        <v>-0.606</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5638000000000001</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1652</v>
+        <v>0.2862</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3985</v>
+        <v>0.2615999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3389</v>
+        <v>-2.3492</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0768</v>
+        <v>-2.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2621</v>
+        <v>-0.2548</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5097</v>
+        <v>-0.4349000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0169</v>
+        <v>-0.9898</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5072000000000001</v>
+        <v>0.5548</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8292</v>
+        <v>-1.9143</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0599</v>
+        <v>-1.1047</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7693</v>
+        <v>-0.8096</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5609</v>
+        <v>1.5521</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2151</v>
+        <v>1.2316</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3458</v>
+        <v>0.3206</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3176</v>
+        <v>0.3327</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3087</v>
+        <v>0.2479</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4094</v>
+        <v>-0.3445</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7181000000000001</v>
+        <v>0.5925</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6136999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4944</v>
+        <v>-1.5207</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9193</v>
+        <v>0.9071</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1497</v>
+        <v>-1.1261</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.769</v>
+        <v>-0.752</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3807</v>
+        <v>-0.3741</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5746</v>
+        <v>0.5124</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7253000000000001</v>
+        <v>-0.7687</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.2812</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2048</v>
+        <v>0.2025000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>1.229</v>
+        <v>1.2148</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2244999999999999</v>
+        <v>0.2216</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5838</v>
+        <v>0.6035</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3593</v>
+        <v>-0.3819</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0162</v>
+        <v>-0.0342</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0786</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.1128</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4653</v>
+        <v>0.4552</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.0399</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4181</v>
+        <v>0.4152</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4458</v>
+        <v>0.4354</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02779999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4181</v>
+        <v>0.4152</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6491</v>
+        <v>-0.6433</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1965</v>
+        <v>-0.1921</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4526</v>
+        <v>-0.4512</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6505000000000001</v>
+        <v>-0.5634000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4654</v>
+        <v>-1.1707</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8148</v>
+        <v>0.6072</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.404</v>
+        <v>-0.4081</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.5009</v>
+        <v>-3.4989</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0968</v>
+        <v>3.0907</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1071</v>
+        <v>0.0212</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0223</v>
+        <v>-1.9413</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9153</v>
+        <v>1.9625</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.297</v>
+        <v>-0.4293</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4785</v>
+        <v>-1.5576</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1816</v>
+        <v>1.1283</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2775</v>
+        <v>3.2393</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.6106</v>
+        <v>-2.5807</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0954</v>
+        <v>-1.049</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5152</v>
+        <v>-1.5316</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2077</v>
+        <v>4.2474</v>
       </c>
       <c r="W9" t="n">
-        <v>4.8583</v>
+        <v>4.9185</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6506</v>
+        <v>-0.6711</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8204999999999996</v>
+        <v>-0.7844000000000007</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7638999999999996</v>
+        <v>0.9899</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5844</v>
+        <v>-1.7745</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1373</v>
+        <v>-1.0798</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1033000000000001</v>
+        <v>-0.1178999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.034</v>
+        <v>-0.9620000000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4656000000000002</v>
+        <v>-0.3192999999999997</v>
       </c>
       <c r="K10" t="n">
-        <v>1.124</v>
+        <v>1.1642</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5894</v>
+        <v>-1.4835</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6718</v>
+        <v>-0.7605999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2273</v>
+        <v>-1.2821</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5555</v>
+        <v>0.5215</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8679</v>
+        <v>2.8343</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6985</v>
+        <v>0.6960999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3468</v>
+        <v>0.3784</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3517</v>
+        <v>0.3176</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2253</v>
+        <v>-2.2227</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9068</v>
+        <v>1.943</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.1321</v>
+        <v>-4.1657</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.888</v>
+        <v>-5.8124</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5081</v>
+        <v>-2.2737</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3798</v>
+        <v>-3.5387</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2229</v>
+        <v>1.2452</v>
       </c>
       <c r="H11" t="n">
-        <v>0.075</v>
+        <v>0.06010000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1479</v>
+        <v>1.1851</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1637</v>
+        <v>3.2777</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9679</v>
+        <v>1.0062</v>
       </c>
       <c r="L11" t="n">
-        <v>2.1959</v>
+        <v>2.2715</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9408</v>
+        <v>-2.0326</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8926999999999999</v>
+        <v>-0.9460999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.048</v>
+        <v>-1.0865</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8922</v>
+        <v>-3.8465</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.1454</v>
+        <v>-6.0736</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8716</v>
+        <v>-1.8517</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.949</v>
+        <v>-0.919</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9226</v>
+        <v>-0.9325</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3471</v>
+        <v>-1.3594</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7698</v>
+        <v>-2.8005</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1208</v>
+        <v>-7.1448</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.076000000000001</v>
+        <v>-4.9938</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0448</v>
+        <v>-2.1511</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4033</v>
+        <v>-1.4189</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8812</v>
+        <v>-0.9079999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5221</v>
+        <v>-0.5109999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0617</v>
+        <v>-2.0296</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6577000000000001</v>
+        <v>-0.6525</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.404</v>
+        <v>-1.3769</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6584</v>
+        <v>0.6106</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2234</v>
+        <v>-0.2553</v>
       </c>
       <c r="O12" t="n">
-        <v>0.882</v>
+        <v>0.8659</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6387</v>
+        <v>1.6197</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5995</v>
+        <v>-1.5812</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9658</v>
+        <v>-0.9398</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6337999999999999</v>
+        <v>-0.6414</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7083</v>
+        <v>-3.7398</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7083</v>
+        <v>-3.7398</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4.128900000000002</v>
+        <v>4.143799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4709</v>
+        <v>8.240600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3424</v>
+        <v>-4.0972</v>
       </c>
       <c r="G13" t="n">
-        <v>7.138800000000002</v>
+        <v>7.1009</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.691400000000001</v>
+        <v>-6.813599999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>13.8301</v>
+        <v>13.9143</v>
       </c>
       <c r="J13" t="n">
-        <v>12.9309</v>
+        <v>13.8376</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0979</v>
+        <v>2.547</v>
       </c>
       <c r="L13" t="n">
-        <v>10.8336</v>
+        <v>11.2908</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.792299999999999</v>
+        <v>-6.7369</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.788699999999999</v>
+        <v>-9.360199999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9971</v>
+        <v>2.6235</v>
       </c>
       <c r="P13" t="n">
-        <v>1.024</v>
+        <v>1.0125</v>
       </c>
       <c r="Q13" t="n">
-        <v>-24.5815</v>
+        <v>-24.2945</v>
       </c>
       <c r="R13" t="n">
-        <v>25.6056</v>
+        <v>25.3069</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.685999999999999</v>
+        <v>-3.6255</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8839999999999997</v>
+        <v>1.1812</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.57</v>
+        <v>-4.8064</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3484000000000012</v>
+        <v>-0.3441000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>17.2377</v>
+        <v>17.5157</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.5859</v>
+        <v>-17.86</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CIUDAD MOLINA BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CIUDAD MOLINA BASKET.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2568</v>
+        <v>6.1841</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4275</v>
+        <v>6.0483</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1707</v>
+        <v>0.1356999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2671999999999999</v>
+        <v>4.8928</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8314999999999999</v>
+        <v>1.2266</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0987</v>
+        <v>3.6662</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5886</v>
+        <v>5.9161</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6669999999999999</v>
+        <v>1.8557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9216</v>
+        <v>4.060499999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3214</v>
+        <v>-1.0233</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4985</v>
+        <v>-0.6289</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1771</v>
+        <v>-0.3943</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8221</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0123</v>
+        <v>-3.0368</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8344</v>
+        <v>3.6441</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3215</v>
+        <v>-0.588</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9651</v>
+        <v>0.2866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3564</v>
+        <v>-0.8747</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8461</v>
+        <v>1.2719</v>
       </c>
       <c r="W2" t="n">
-        <v>3.886</v>
+        <v>2.8822</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.04</v>
+        <v>-1.6103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4058</v>
+        <v>4.4935</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8407</v>
+        <v>5.7907</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4348999999999998</v>
+        <v>-1.2972</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8928</v>
+        <v>0.2671999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2266</v>
+        <v>-0.8314999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6662</v>
+        <v>1.0987</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9161</v>
+        <v>1.5886</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8557</v>
+        <v>0.6669999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>4.060499999999999</v>
+        <v>0.9216</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0233</v>
+        <v>-1.3214</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6289</v>
+        <v>-1.4985</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3943</v>
+        <v>0.1771</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6073999999999999</v>
+        <v>1.8221</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0368</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6441</v>
+        <v>2.8344</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3663</v>
+        <v>1.5581</v>
       </c>
       <c r="T3" t="n">
-        <v>0.07900000000000001</v>
+        <v>1.3284</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4453</v>
+        <v>0.2299</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2719</v>
+        <v>0.8461</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8822</v>
+        <v>3.886</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6103</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9147</v>
+        <v>3.8002</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5283</v>
+        <v>0.5923</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3864</v>
+        <v>3.2079</v>
       </c>
       <c r="G4" t="n">
         <v>1.9998</v>
@@ -766,13 +766,13 @@
         <v>3.4417</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2266</v>
+        <v>0.112</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0376</v>
+        <v>0.1016</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1889</v>
+        <v>0.0104</v>
       </c>
       <c r="V4" t="n">
         <v>1.2834</v>
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.109900000000001</v>
+        <v>2.3407</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8721</v>
+        <v>2.0797</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2378</v>
+        <v>0.2610000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>4.110399999999999</v>
@@ -844,13 +844,13 @@
         <v>1.8221</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6202</v>
+        <v>-1.3894</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0141</v>
+        <v>-0.8065</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.606</v>
+        <v>-0.5828</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1902</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2862</v>
+        <v>-0.4197</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2615999999999999</v>
+        <v>1.2066</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3492</v>
+        <v>-0.4081</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0944</v>
+        <v>-3.4989</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2548</v>
+        <v>3.0907</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4349000000000001</v>
+        <v>0.0212</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9898</v>
+        <v>-1.9413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5548</v>
+        <v>1.9625</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9143</v>
+        <v>-0.4293</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1047</v>
+        <v>-1.5576</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8096</v>
+        <v>1.1283</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0123</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0123</v>
+        <v>-5.0613</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0246</v>
+        <v>3.2393</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5521</v>
+        <v>-1.2302</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2316</v>
+        <v>-0.2981</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3206</v>
+        <v>-0.9322</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3327</v>
+        <v>4.2474</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5019</v>
+        <v>4.9185</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1692</v>
+        <v>-0.6711</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2479</v>
+        <v>0.7393000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3445</v>
+        <v>0.3105</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5925</v>
+        <v>0.4288</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6136999999999999</v>
+        <v>-2.3492</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5207</v>
+        <v>-2.0944</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9071</v>
+        <v>-0.2548</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1261</v>
+        <v>-0.4349000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.752</v>
+        <v>-0.9898</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3741</v>
+        <v>0.5548</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5124</v>
+        <v>-1.9143</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7687</v>
+        <v>-1.1047</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2812</v>
+        <v>-0.8096</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2025000000000001</v>
+        <v>1.0123</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2148</v>
+        <v>2.0246</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2216</v>
+        <v>1.7437</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6035</v>
+        <v>1.2558</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3819</v>
+        <v>0.4878</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4374</v>
+        <v>0.3327</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1902</v>
+        <v>0.5019</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7528</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0342</v>
+        <v>0.1273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0786</v>
+        <v>0.1825</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1128</v>
+        <v>-0.0552</v>
       </c>
       <c r="G8" t="n">
         <v>0.4552</v>
@@ -1078,13 +1078,13 @@
         <v>0.4049</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6433</v>
+        <v>-0.4819</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1921</v>
+        <v>-0.0883</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4512</v>
+        <v>-0.3935999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2509</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5634000000000001</v>
+        <v>-0.2243</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1707</v>
+        <v>-0.6958</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6072</v>
+        <v>0.4715</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4081</v>
+        <v>-0.6136999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.4989</v>
+        <v>-1.5207</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0907</v>
+        <v>0.9071</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0212</v>
+        <v>-1.1261</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9413</v>
+        <v>-0.752</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9625</v>
+        <v>-0.3741</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4293</v>
+        <v>0.5124</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5576</v>
+        <v>-0.7687</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1283</v>
+        <v>1.2812</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8221</v>
+        <v>0.2025000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.0613</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2393</v>
+        <v>1.2148</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.5807</v>
+        <v>-0.2505000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.049</v>
+        <v>0.2523</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5316</v>
+        <v>-0.5028</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2474</v>
+        <v>0.4374</v>
       </c>
       <c r="W9" t="n">
-        <v>4.9185</v>
+        <v>1.1902</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6711</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7844000000000007</v>
+        <v>-0.9831000000000003</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9899</v>
+        <v>0.8066</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7745</v>
+        <v>-1.7897</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0798</v>
@@ -1234,13 +1234,13 @@
         <v>2.8343</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6960999999999999</v>
+        <v>0.4974</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3784</v>
+        <v>0.1951</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3176</v>
+        <v>0.3024</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2227</v>
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8124</v>
+        <v>-4.0651</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2737</v>
+        <v>-0.9241999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5387</v>
+        <v>-3.1409</v>
       </c>
       <c r="G11" t="n">
         <v>1.2452</v>
@@ -1312,13 +1312,13 @@
         <v>2.227</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8517</v>
+        <v>-0.1043</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.919</v>
+        <v>0.4305</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9325</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3594</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1448</v>
+        <v>-6.9834</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9938</v>
+        <v>-4.890000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1511</v>
+        <v>-2.0934</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4189</v>
@@ -1390,13 +1390,13 @@
         <v>1.6197</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5812</v>
+        <v>-1.4197</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9398</v>
+        <v>-0.836</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6414</v>
+        <v>-0.5837</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7398</v>
@@ -1423,16 +1423,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4.143799999999999</v>
+        <v>6.216200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>8.240600000000001</v>
+        <v>8.880899999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0972</v>
+        <v>-2.6649</v>
       </c>
       <c r="G13" t="n">
-        <v>7.1009</v>
+        <v>7.100899999999998</v>
       </c>
       <c r="H13" t="n">
         <v>-6.813599999999999</v>
@@ -1444,7 +1444,7 @@
         <v>13.8376</v>
       </c>
       <c r="K13" t="n">
-        <v>2.547</v>
+        <v>2.547000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>11.2908</v>
@@ -1459,7 +1459,7 @@
         <v>2.6235</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0125</v>
+        <v>1.012499999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-24.2945</v>
@@ -1468,13 +1468,13 @@
         <v>25.3069</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6255</v>
+        <v>-1.5528</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1812</v>
+        <v>1.8214</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.8064</v>
+        <v>-3.3741</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3441000000000001</v>
